--- a/TeplosilaWeb/Content/properties/htrv3r.xlsx
+++ b/TeplosilaWeb/Content/properties/htrv3r.xlsx
@@ -8,26 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pge27\OneDrive\Рабочий стол\TeploSilaWeb\TeplosilaWeb\Content\properties\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14A63456-B92C-46D8-89B6-A7AE6FC5DA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6802FABF-77BE-41D0-ACE3-AE0FE88386E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5025" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -141,15 +132,6 @@
     <t>Наличие функции безопасности (возврат)</t>
   </si>
   <si>
-    <t>TSL-1600-25-2-24-IP67</t>
-  </si>
-  <si>
-    <t>TSL-2200-40-2-24-IP67</t>
-  </si>
-  <si>
-    <t>TSL-3000-60-2-24-IP67</t>
-  </si>
-  <si>
     <t>TRV-3 разделительный</t>
   </si>
   <si>
@@ -181,6 +163,15 @@
   </si>
   <si>
     <t>TSL-3000-60-2T-230-IP67</t>
+  </si>
+  <si>
+    <t>TSL-1600-25-2М-24-IP67</t>
+  </si>
+  <si>
+    <t>TSL-2200-40-2М-24-IP67</t>
+  </si>
+  <si>
+    <t>TSL-3000-60-2М-24-IP67</t>
   </si>
 </sst>
 </file>
@@ -709,7 +700,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -915,7 +906,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C6" s="6">
         <v>8</v>
@@ -1033,7 +1024,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C8" s="6">
         <v>8</v>
@@ -1092,7 +1083,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C9" s="12">
         <v>8</v>
@@ -1210,7 +1201,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C11" s="6">
         <v>8</v>
@@ -1328,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C13" s="12">
         <v>8</v>
@@ -1446,7 +1437,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -1499,7 +1490,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
@@ -1556,7 +1547,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
@@ -1609,7 +1600,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
@@ -1715,7 +1706,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -1821,7 +1812,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -1927,7 +1918,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -1978,7 +1969,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
@@ -2230,6 +2221,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:N3"/>
     <mergeCell ref="C4:N4"/>
     <mergeCell ref="A1:W1"/>
@@ -2246,7 +2238,6 @@
     <mergeCell ref="Q3:Q5"/>
     <mergeCell ref="R3:R5"/>
     <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:B5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/TeplosilaWeb/Content/properties/htrv3r.xlsx
+++ b/TeplosilaWeb/Content/properties/htrv3r.xlsx
@@ -1,27 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pge27\OneDrive\Рабочий стол\TeploSilaWeb\TeplosilaWeb\Content\properties\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user29\Documents\ТЗ программа подбора TRV, RDT\ТЗ клапаны TRV\25.05.2026 (действ)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6802FABF-77BE-41D0-ACE3-AE0FE88386E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42B3DCF-5477-40A0-A524-1DF3E260DEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -178,7 +184,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,34 +232,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -337,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -359,28 +343,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -392,7 +358,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -400,9 +366,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -687,62 +650,62 @@
   <dimension ref="A1:W29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
-    <col min="3" max="14" width="4.5703125" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" customWidth="1"/>
-    <col min="19" max="19" width="10.140625" customWidth="1"/>
-    <col min="20" max="20" width="11.140625" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" customWidth="1"/>
-    <col min="22" max="22" width="12" customWidth="1"/>
-    <col min="23" max="23" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="4" customWidth="1"/>
+    <col min="3" max="14" width="4.5703125" style="4" customWidth="1"/>
+    <col min="15" max="17" width="9.140625" style="4"/>
+    <col min="18" max="18" width="13.5703125" style="4" customWidth="1"/>
+    <col min="19" max="19" width="10.140625" style="4" customWidth="1"/>
+    <col min="20" max="20" width="11.140625" style="4" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="4" customWidth="1"/>
+    <col min="22" max="22" width="12" style="4" customWidth="1"/>
+    <col min="23" max="23" width="13.28515625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
       <c r="B2" s="1">
         <v>53</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C2" s="16">
         <v>54</v>
       </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1">
         <v>55</v>
@@ -773,88 +736,88 @@
       </c>
     </row>
     <row r="3" spans="1:23" s="5" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="21" t="s">
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="R3" s="21" t="s">
+      <c r="P3" s="15"/>
+      <c r="Q3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="R3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="S3" s="23" t="s">
+      <c r="S3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="T3" s="23"/>
-      <c r="U3" s="23" t="s">
+      <c r="T3" s="15"/>
+      <c r="U3" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="V3" s="21" t="s">
+      <c r="V3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="W3" s="21" t="s">
+      <c r="W3" s="15" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:23" s="5" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="17" t="s">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="21" t="s">
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="21" t="s">
+      <c r="P4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="23" t="s">
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="T4" s="23" t="s">
+      <c r="T4" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="U4" s="23"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="21"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
     </row>
     <row r="5" spans="1:23" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="15"/>
       <c r="C5" s="2">
         <v>15</v>
       </c>
@@ -891,15 +854,15 @@
       <c r="N5" s="2">
         <v>200</v>
       </c>
-      <c r="O5" s="21"/>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="23"/>
-      <c r="T5" s="23"/>
-      <c r="U5" s="23"/>
-      <c r="V5" s="21"/>
-      <c r="W5" s="21"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
     </row>
     <row r="6" spans="1:23" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
@@ -1079,61 +1042,61 @@
       </c>
     </row>
     <row r="9" spans="1:23" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="12">
+      <c r="A9" s="6">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="12">
-        <v>8</v>
-      </c>
-      <c r="D9" s="12">
-        <v>8</v>
-      </c>
-      <c r="E9" s="12">
-        <v>8</v>
-      </c>
-      <c r="F9" s="12">
+      <c r="C9" s="6">
+        <v>8</v>
+      </c>
+      <c r="D9" s="6">
+        <v>8</v>
+      </c>
+      <c r="E9" s="6">
+        <v>8</v>
+      </c>
+      <c r="F9" s="6">
         <v>7</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="6">
         <v>4</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="6">
         <v>2.9</v>
       </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="P9" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q9" s="12">
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q9" s="6">
         <v>1600</v>
       </c>
-      <c r="R9" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="S9" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T9" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="U9" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V9" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="W9" s="12">
+      <c r="R9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="S9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="T9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="U9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="V9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="W9" s="6">
         <v>10</v>
       </c>
     </row>
@@ -1227,31 +1190,31 @@
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
-      <c r="O11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q11" s="9">
+      <c r="O11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q11" s="6">
         <v>2200</v>
       </c>
-      <c r="R11" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="S11" s="9" t="s">
+      <c r="R11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="S11" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="T11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="U11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="V11" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="W11" s="9">
+      <c r="T11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="V11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="W11" s="6">
         <v>10</v>
       </c>
     </row>
@@ -1286,90 +1249,90 @@
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
-      <c r="O12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q12" s="9">
+      <c r="O12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q12" s="6">
         <v>1600</v>
       </c>
-      <c r="R12" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="S12" s="9" t="s">
+      <c r="R12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="S12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="T12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="U12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="V12" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="W12" s="9">
+      <c r="T12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="U12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="V12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="W12" s="6">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:23" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="12">
-        <v>8</v>
-      </c>
-      <c r="B13" s="13" t="s">
+      <c r="A13" s="6">
+        <v>8</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="12">
-        <v>8</v>
-      </c>
-      <c r="D13" s="12">
-        <v>8</v>
-      </c>
-      <c r="E13" s="12">
-        <v>8</v>
-      </c>
-      <c r="F13" s="12">
-        <v>8</v>
-      </c>
-      <c r="G13" s="12">
+      <c r="C13" s="6">
+        <v>8</v>
+      </c>
+      <c r="D13" s="6">
+        <v>8</v>
+      </c>
+      <c r="E13" s="6">
+        <v>8</v>
+      </c>
+      <c r="F13" s="6">
+        <v>8</v>
+      </c>
+      <c r="G13" s="6">
         <v>6</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="6">
         <v>4</v>
       </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="P13" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q13" s="12">
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q13" s="6">
         <v>2200</v>
       </c>
-      <c r="R13" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="S13" s="12" t="s">
+      <c r="R13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="S13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="T13" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="U13" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="V13" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="W13" s="12">
+      <c r="T13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="U13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="V13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="W13" s="6">
         <v>10</v>
       </c>
     </row>
@@ -1448,10 +1411,10 @@
       <c r="I15" s="6">
         <v>4.5</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="9">
         <v>2.75</v>
       </c>
-      <c r="K15" s="11">
+      <c r="K15" s="9">
         <v>1.75</v>
       </c>
       <c r="L15" s="6"/>
@@ -1486,59 +1449,59 @@
       </c>
     </row>
     <row r="16" spans="1:23" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="12">
+      <c r="A16" s="6">
         <v>11</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6">
         <v>4.5</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="9">
         <v>2.75</v>
       </c>
-      <c r="K16" s="15">
+      <c r="K16" s="9">
         <v>1.75</v>
       </c>
-      <c r="L16" s="15">
+      <c r="L16" s="9">
         <v>1.25</v>
       </c>
-      <c r="M16" s="15">
+      <c r="M16" s="9">
         <v>0.75</v>
       </c>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="P16" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q16" s="12">
+      <c r="N16" s="6"/>
+      <c r="O16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q16" s="6">
         <v>3000</v>
       </c>
-      <c r="R16" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="S16" s="12" t="s">
+      <c r="R16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="S16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="T16" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="U16" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V16" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="W16" s="12">
+      <c r="T16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="U16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="V16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="W16" s="6">
         <v>12</v>
       </c>
     </row>
@@ -1596,55 +1559,55 @@
       </c>
     </row>
     <row r="18" spans="1:23" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="12">
-        <v>13</v>
-      </c>
-      <c r="B18" s="13" t="s">
+      <c r="A18" s="6">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6">
         <v>3</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="6">
         <v>2.1</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="6">
         <v>1.3</v>
       </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="P18" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q18" s="12">
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q18" s="6">
         <v>2200</v>
       </c>
-      <c r="R18" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="S18" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T18" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V18" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="W18" s="12">
+      <c r="R18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="S18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="T18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="U18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="V18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="W18" s="6">
         <v>10</v>
       </c>
     </row>
@@ -1717,40 +1680,40 @@
       <c r="I20" s="6">
         <v>4.5</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="9">
         <v>2.75</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="9">
         <v>1.75</v>
       </c>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
-      <c r="O20" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="P20" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q20" s="9">
+      <c r="O20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q20" s="6">
         <v>3000</v>
       </c>
-      <c r="R20" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="S20" s="9" t="s">
+      <c r="R20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="S20" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="T20" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="U20" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="V20" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="W20" s="9">
+      <c r="T20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="U20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="V20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="W20" s="6">
         <v>12</v>
       </c>
     </row>
@@ -1779,84 +1742,84 @@
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
-      <c r="O21" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="P21" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q21" s="9">
+      <c r="O21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q21" s="6">
         <v>2200</v>
       </c>
-      <c r="R21" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="S21" s="9" t="s">
+      <c r="R21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="S21" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="T21" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="U21" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="V21" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="W21" s="9">
+      <c r="T21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="U21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="V21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="W21" s="6">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:23" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A22" s="12">
+      <c r="A22" s="6">
         <v>17</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12">
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6">
         <v>4.5</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="9">
         <v>2.75</v>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="9">
         <v>1.75</v>
       </c>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="P22" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q22" s="12">
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q22" s="6">
         <v>3000</v>
       </c>
-      <c r="R22" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="S22" s="12" t="s">
+      <c r="R22" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="S22" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="T22" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="U22" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="V22" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="W22" s="12">
+      <c r="T22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="U22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="V22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="W22" s="6">
         <v>12</v>
       </c>
     </row>
@@ -1929,10 +1892,10 @@
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
-      <c r="L24" s="11">
+      <c r="L24" s="9">
         <v>1.25</v>
       </c>
-      <c r="M24" s="11">
+      <c r="M24" s="9">
         <v>0.75</v>
       </c>
       <c r="N24" s="6"/>
@@ -1965,53 +1928,53 @@
       </c>
     </row>
     <row r="25" spans="1:23" s="8" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="12">
+      <c r="A25" s="6">
         <v>20</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="15">
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="9">
         <v>1.25</v>
       </c>
-      <c r="M25" s="15">
+      <c r="M25" s="9">
         <v>0.75</v>
       </c>
-      <c r="N25" s="12"/>
-      <c r="O25" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="P25" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q25" s="16">
+      <c r="N25" s="6"/>
+      <c r="O25" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="P25" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q25" s="10">
         <v>3000</v>
       </c>
-      <c r="R25" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="S25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="T25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="U25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="V25" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="W25" s="12">
+      <c r="R25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="S25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="T25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="U25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="V25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="W25" s="6">
         <v>12</v>
       </c>
     </row>
@@ -2031,38 +1994,38 @@
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
       <c r="K26" s="6"/>
-      <c r="L26" s="11">
+      <c r="L26" s="9">
         <v>1.25</v>
       </c>
-      <c r="M26" s="11">
+      <c r="M26" s="9">
         <v>0.75</v>
       </c>
       <c r="N26" s="6"/>
-      <c r="O26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="P26" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q26" s="9">
+      <c r="O26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q26" s="6">
         <v>3000</v>
       </c>
-      <c r="R26" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="S26" s="9" t="s">
+      <c r="R26" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="S26" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="T26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="U26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="V26" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="W26" s="9">
+      <c r="T26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="U26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="V26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="W26" s="6">
         <v>12</v>
       </c>
     </row>
@@ -2082,10 +2045,10 @@
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
-      <c r="L27" s="11">
+      <c r="L27" s="9">
         <v>1.25</v>
       </c>
-      <c r="M27" s="11">
+      <c r="M27" s="9">
         <v>0.75</v>
       </c>
       <c r="N27" s="6"/>
@@ -2188,34 +2151,34 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
-      <c r="N29" s="11">
+      <c r="N29" s="9">
         <v>0.75</v>
       </c>
-      <c r="O29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="P29" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q29" s="9">
+      <c r="O29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q29" s="6">
         <v>5000</v>
       </c>
-      <c r="R29" s="10" t="s">
+      <c r="R29" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="S29" s="9" t="s">
+      <c r="S29" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="T29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="U29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="V29" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="W29" s="9">
+      <c r="T29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="U29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="V29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="W29" s="6">
         <v>30</v>
       </c>
     </row>
